--- a/TESTS/zlit_7_bykov.xlsx
+++ b/TESTS/zlit_7_bykov.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Василь Биков — білоруський письменник один з найвидатніших авторів прози про Другу світову</t>
+          <t>Василь Биков</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>«Лейтенантська проза» — белетристика про Другу світову очима рядових солдатів без прикрас і пафосу</t>
+          <t>«Лейтенантська проза»</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>В Альпах в кінці Другої світової — втеча радянського солдата Івана і італійки Джулії з нацистського табору</t>
+          <t>В Альпах в кінці Другої світової</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Іван Терешка — білоруський солдат і Джулія Новеллі — молода італійська дівчина</t>
+          <t>Іван Терешка</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Спільна втеча з нацистського концентраційного табору — небезпека змушує незнайомців стати єдиним цілим</t>
+          <t>Спільна втеча з нацистського концентраційного табору</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Вони говорять різними мовами і майже не розуміють один одного — але людяність і почуття перевершують мовний бар'єр</t>
+          <t>Вони говорять різними мовами і майже не розуміють один одного</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Від взаємної недовіри до щирої любові — три дні у горах змінюють обох назавжди</t>
+          <t>Від взаємної недовіри до щирої любові</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Простір свободи і очищення — на висоті далеко від жаху війни двоє людей відкривають справжнє</t>
+          <t>Простір свободи і очищення</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Він рятує Джулію жертвуючи собою — прикриває її відступ і гине щоб вона вижила</t>
+          <t>Він рятує Джулію жертвуючи собою</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Як Іван Терешка опинився в німецькому концтаборі в Альпах?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Добровільно здався</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Потрапив у полон як радянський військовополонений і був вивезений на примусові роботи</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Приїхав туристом</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Народився там</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Яким було життя Івана в таборі до втечі?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Легким</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Виснажлива примусова праця, голод і постійна загроза смерті</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був охоронцем</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він жив окремо у комфорті</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Що остаточно підштовхнуло Івана до рішення тікати, попри ризик?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Наказ командира</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розуміння, що залишитись означає неминучу смерть, тож краще загинути, намагаючись вирватись на волю</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Допомога охоронців</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лист з дому</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Коли і як Іван та Джулія здійснили втечу з табору?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вдень, через головні ворота</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Скориставшись метушнею в таборі, вони вислизнули з-під охорони</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>На машині</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Підземним тунелем, який рили місяцями</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Чому саме Джулія опинилась поруч з Іваном під час втечі?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони давно дружили</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона також була в'язнем табору, італійкою, і втекла одночасно з ним, опинившись поруч випадково</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона допомагала охоронцям</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона шукала Івана спеціально</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Куди тікачі прямували після втечі з табору?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>До найближчого міста</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У гори — Альпи, сподіваючись знайти прихисток і вибратись на волю</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>До моря</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Назад у табір</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Хто переслідував Івана і Джулію після втечі?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Місцева поліція</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Німецька охорона з собаками, що йшла слідом по їхньому запаху</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Інші втікачі-конкуренти</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніхто, втеча залишилась непоміченою</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як втікачі намагались позбутись переслідувачів-собак?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Билися з ними</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Намагались збити слід — переходили через воду й скелясту місцевість</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сховались у будинку</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Підкупили охорону</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Яку загрозу для втікачів становила сама гірська місцевість Альп, окрім переслідувачів?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Жодної, лише краса</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Холод, круті схили й нестача їжі — природа сама була небезпечним супротивником</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дикі звірі</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Туристи</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Як Іван і Джулія, не знаючи мови одне одного, поступово почали розуміти один одного?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Через перекладача</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Через жести, інтонації, спільні дії і поступово — кілька слів кожною мовою</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони одразу заговорили однією мовою</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони не спілкувались взагалі</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що Іван і Джулія робили, щоб роздобути їжу під час втечі в горах?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Купували в селах</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Шукали дику їжу — ягоди, коренеплоди на покинутих полях, іноді ризикуючи наближатись до людей</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Просили місцевих відкрито</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Полювали зі зброєю</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Як змінювалось ставлення Джулії до Івана протягом спільної втечі?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишалось байдужим</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Від обережності й недовіри до незнайомця — до глибокої довіри, прив'язаності й кохання</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона почала боятися його ще більше</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона намагалась його позбутись</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Яку небезпечну ділянку шляху Іван і Джулія мусили подолати в горах?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Рівну дорогу</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Крутий, небезпечний переїзд через скелі чи ущелину, де ризикували зірватись</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Підземний тунель</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Річку на човні</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Як Іван допомагав Джулії в найважчі моменти подорожі?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Йшов окремо, не звертаючи уваги</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Підтримував її фізично і морально, ділився останніми силами й їжею</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Покинув її, щоб рятуватись самому</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Наказував їй усе робити самій</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Чому, попри постійну небезпеку, ці дні в горах стали для героїв особливими?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони нічого не відчували, крім страху</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Попри жах втечі, вони вперше за довгий час відчули себе вільними людьми, а не бранцями</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Їм було байдуже</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони сварились весь час</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що сталося, коли переслідувачі з собаками наздогнали втікачів наприкінці повісті?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Усі мирно розійшлись</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Іван залишився прикривати Джулію, даючи їй шанс утекти, поки сам бився з переслідувачами</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Обох одразу схопили</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Переслідувачі здалися</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Яким було рішення Івана в останній критичний момент?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Здатись разом з Джулією</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Свідомо пожертвувати власним життям, аби Джулія встигла дістатись до своїх</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Втекти, кинувши Джулію</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Заховатись і чекати</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Що сталося з Іваном у фінальній сутичці?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він вижив без поранень</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він гине, борючись з ворогами та псом, але здобуває для Джулії шанс на життя</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його взяли в полон</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він зник безвісти, але живий</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Як читач дізнається про подальшу долю Джулії після подій повісті?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>З розповіді самого Івана</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Через лист Джулії, написаний роками пізніше, що завершує повість</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>З газетної статті</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Її доля лишається невідомою повністю</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Про що йдеться в листі Джулії наприкінці повісті?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Про її нове життя без жодного зв'язку з минулим</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона згадує Івана з вдячністю і любов'ю, натякаючи на сина, народженого після тих подій</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Про те, що вона забула Івана</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Про повернення до табору</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Як лист Джулії впливає на сприйняття всієї повісті читачем?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не змінює</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він надає трагічній історії відтінок надії — життя й любов тривають навіть після смерті героя</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Робить історію ще сумнішою без надії</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Виявляється, що все було вигадкою Джулії</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яка роль трьох днів втечі для розвитку образів героїв?</t>
+          <t>Три дні втечі в горах — це час, протягом якого і Іван, і Джулія розкриваються по-новому, переживаючи інтенсивні зміни в стосунках і поглядах.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між «Альпійською баладою» і баладою як жанром?</t>
+          <t>Назва «Альпійська балада» вказує на поєднання ліричного й трагічного начала, типове для жанру балади.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яке місце займає «Альпійська балада» у білоруській літературі?</t>
+          <t>«Альпійська балада» Бикова не належить до значущих творів білоруської літератури про війну.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Що таке «лейтенантська проза» і ким є Биков у цьому контексті?</t>
+          <t>«Лейтенантська проза» показує війну очима простого учасника, а не командування; Биков — один з її представників.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка роль листа Джулії у фіналі повісті?</t>
+          <t>Лист Джулії у фіналі підтверджує, що історія Івана й Джулії не була забута і має продовження в житті.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яку антивоєнну позицію займає Биков?</t>
+          <t>Биков у «Альпійській баладі» прославляє війну як шлях до героїчної слави.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які теми розкриває «Альпійська балада»?</t>
+          <t>Що відбувається у повісті «Альпійська балада»?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Кохання в умовах війни</t>
+          <t>Іван і Джулія тікають з концтабору</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Людяність що долає бар'єри мови і культури</t>
+          <t>Їх переслідують з собаками</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Прославляння радянської армії</t>
+          <t>Іван здається ворогам без боротьби</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Жертовність заради іншого</t>
+          <t>Іван гине, рятуючи Джулію</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2337,6 +2539,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Вона показує людину а не «гвинтик» — особисте кохання і трагедію окремої особи а не масовий героїзм</t>
+          <t>Вона показує людину а не «гвинтик»</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
